--- a/CaseII.xlsx
+++ b/CaseII.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\论文\02 Trans Smart Grid\00 程序汇总\Hydraulic-Transients-and-Thermal-Dynamics-Embedded-Contingency-Analysis-of-Integrated-Electricity-and-Heating-Systems\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3BD70E2-4182-4853-8EA3-9BD1DAD7F8E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="8"/>
+    <workbookView xWindow="38280" yWindow="-4035" windowWidth="16440" windowHeight="28320" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pipe" sheetId="6" r:id="rId1"/>
@@ -26,16 +32,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="158">
   <si>
     <t>No.</t>
   </si>
@@ -69,7 +76,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>Sup (</t>
     </r>
@@ -78,7 +85,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Segoe UI Symbol"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>℃</t>
     </r>
@@ -87,7 +94,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>)</t>
     </r>
@@ -98,7 +105,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>Ret (</t>
     </r>
@@ -107,7 +114,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Segoe UI Symbol"/>
-        <charset val="134"/>
+        <family val="2"/>
       </rPr>
       <t>℃</t>
     </r>
@@ -116,7 +123,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Times New Roman"/>
-        <charset val="134"/>
+        <family val="1"/>
       </rPr>
       <t>)</t>
     </r>
@@ -326,9 +333,6 @@
     <t>-0.710473706241255</t>
   </si>
   <si>
-    <t>0.00370300000000000</t>
-  </si>
-  <si>
     <t>0.0181010000000000</t>
   </si>
   <si>
@@ -350,9 +354,6 @@
     <t>-0.0387930000000000</t>
   </si>
   <si>
-    <t>0.0179000000000000</t>
-  </si>
-  <si>
     <t>0.0942000000000000</t>
   </si>
   <si>
@@ -368,18 +369,12 @@
     <t>-0.0410000000000000</t>
   </si>
   <si>
-    <t>0.0143180000000000</t>
-  </si>
-  <si>
     <t>0.0720270000000000</t>
   </si>
   <si>
     <t>-0.108237000000000</t>
   </si>
   <si>
-    <t>0.0150290000000000</t>
-  </si>
-  <si>
     <t>0.0601140000000000</t>
   </si>
   <si>
@@ -456,9 +451,6 @@
   </si>
   <si>
     <t>-0.0325000000000000</t>
-  </si>
-  <si>
-    <t>0.00450900000000000</t>
   </si>
   <si>
     <t>0.0180340000000000</t>
@@ -581,14 +573,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -600,373 +586,51 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -974,251 +638,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1258,61 +680,17 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1570,23 +948,23 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J133"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="9" style="8"/>
     <col min="4" max="4" width="8.125" style="8" customWidth="1"/>
     <col min="5" max="6" width="9" style="8"/>
-    <col min="7" max="7" width="10.5833333333333" style="8" customWidth="1"/>
+    <col min="7" max="7" width="10.625" style="8" customWidth="1"/>
     <col min="8" max="8" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1612,7 +990,7 @@
       <c r="I1" s="9"/>
       <c r="J1" s="11"/>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="8">
         <v>1</v>
       </c>
@@ -1629,15 +1007,15 @@
         <v>1.2</v>
       </c>
       <c r="F2" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G2" s="8">
-        <v>2.08776</v>
+        <v>2.0877599999999998</v>
       </c>
       <c r="H2" s="10"/>
       <c r="I2" s="12"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
         <v>2</v>
       </c>
@@ -1654,15 +1032,15 @@
         <v>0.4</v>
       </c>
       <c r="F3" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G3" s="8">
-        <v>2.08917</v>
+        <v>2.0891700000000002</v>
       </c>
       <c r="H3" s="10"/>
       <c r="I3" s="12"/>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="8">
         <v>3</v>
       </c>
@@ -1676,18 +1054,18 @@
         <v>7664</v>
       </c>
       <c r="E4" s="8">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F4" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G4" s="8">
-        <v>2.08788</v>
+        <v>2.0878800000000002</v>
       </c>
       <c r="H4" s="10"/>
       <c r="I4" s="12"/>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
         <v>4</v>
       </c>
@@ -1704,15 +1082,15 @@
         <v>0.4</v>
       </c>
       <c r="F5" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G5" s="8">
-        <v>2.08884</v>
+        <v>2.0888399999999998</v>
       </c>
       <c r="H5" s="10"/>
       <c r="I5" s="12"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
         <v>5</v>
       </c>
@@ -1729,7 +1107,7 @@
         <v>0.3</v>
       </c>
       <c r="F6" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G6" s="8">
         <v>2.0884</v>
@@ -1737,7 +1115,7 @@
       <c r="H6" s="10"/>
       <c r="I6" s="12"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="8">
         <v>6</v>
       </c>
@@ -1751,18 +1129,18 @@
         <v>910</v>
       </c>
       <c r="E7" s="8">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F7" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G7" s="8">
-        <v>2.08797</v>
+        <v>2.0879699999999999</v>
       </c>
       <c r="H7" s="10"/>
       <c r="I7" s="12"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="8">
         <v>7</v>
       </c>
@@ -1776,10 +1154,10 @@
         <v>705</v>
       </c>
       <c r="E8" s="8">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F8" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G8" s="8">
         <v>2.08799</v>
@@ -1787,7 +1165,7 @@
       <c r="H8" s="10"/>
       <c r="I8" s="12"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>8</v>
       </c>
@@ -1801,18 +1179,18 @@
         <v>973</v>
       </c>
       <c r="E9" s="8">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F9" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G9" s="8">
-        <v>2.08801</v>
+        <v>2.0880100000000001</v>
       </c>
       <c r="H9" s="10"/>
       <c r="I9" s="12"/>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="8">
         <v>9</v>
       </c>
@@ -1829,7 +1207,7 @@
         <v>0.5</v>
       </c>
       <c r="F10" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G10" s="8">
         <v>2.08839</v>
@@ -1837,7 +1215,7 @@
       <c r="H10" s="10"/>
       <c r="I10" s="12"/>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>10</v>
       </c>
@@ -1854,7 +1232,7 @@
         <v>0.5</v>
       </c>
       <c r="F11" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G11" s="8">
         <v>2.08982</v>
@@ -1862,7 +1240,7 @@
       <c r="H11" s="10"/>
       <c r="I11" s="12"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>11</v>
       </c>
@@ -1879,15 +1257,15 @@
         <v>0.8</v>
       </c>
       <c r="F12" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G12" s="8">
-        <v>2.08804</v>
+        <v>2.0880399999999999</v>
       </c>
       <c r="H12" s="10"/>
       <c r="I12" s="12"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>12</v>
       </c>
@@ -1904,15 +1282,15 @@
         <v>0.3</v>
       </c>
       <c r="F13" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G13" s="8">
-        <v>2.08817</v>
+        <v>2.0881699999999999</v>
       </c>
       <c r="H13" s="10"/>
       <c r="I13" s="12"/>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>13</v>
       </c>
@@ -1926,18 +1304,18 @@
         <v>612</v>
       </c>
       <c r="E14" s="8">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F14" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G14" s="8">
-        <v>2.08809</v>
+        <v>2.0880899999999998</v>
       </c>
       <c r="H14" s="10"/>
       <c r="I14" s="12"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>14</v>
       </c>
@@ -1951,18 +1329,18 @@
         <v>650</v>
       </c>
       <c r="E15" s="8">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F15" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G15" s="8">
-        <v>2.08808</v>
+        <v>2.0880800000000002</v>
       </c>
       <c r="H15" s="10"/>
       <c r="I15" s="12"/>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="8">
         <v>15</v>
       </c>
@@ -1976,10 +1354,10 @@
         <v>922</v>
       </c>
       <c r="E16" s="8">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F16" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G16" s="8">
         <v>2.08812</v>
@@ -1987,7 +1365,7 @@
       <c r="H16" s="10"/>
       <c r="I16" s="12"/>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="8">
         <v>16</v>
       </c>
@@ -2004,15 +1382,15 @@
         <v>0.8</v>
       </c>
       <c r="F17" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G17" s="8">
-        <v>2.08817</v>
+        <v>2.0881699999999999</v>
       </c>
       <c r="H17" s="10"/>
       <c r="I17" s="12"/>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="8">
         <v>17</v>
       </c>
@@ -2029,15 +1407,15 @@
         <v>1</v>
       </c>
       <c r="F18" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G18" s="8">
-        <v>2.08821</v>
+        <v>2.0882100000000001</v>
       </c>
       <c r="H18" s="10"/>
       <c r="I18" s="12"/>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="8">
         <v>18</v>
       </c>
@@ -2054,15 +1432,15 @@
         <v>1</v>
       </c>
       <c r="F19" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G19" s="8">
-        <v>2.08824</v>
+        <v>2.0882399999999999</v>
       </c>
       <c r="H19" s="10"/>
       <c r="I19" s="12"/>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="8">
         <v>19</v>
       </c>
@@ -2079,15 +1457,15 @@
         <v>0.8</v>
       </c>
       <c r="F20" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G20" s="8">
-        <v>2.08828</v>
+        <v>2.0882800000000001</v>
       </c>
       <c r="H20" s="10"/>
       <c r="I20" s="12"/>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="8">
         <v>20</v>
       </c>
@@ -2104,7 +1482,7 @@
         <v>0.8</v>
       </c>
       <c r="F21" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G21" s="8">
         <v>2.08832</v>
@@ -2112,7 +1490,7 @@
       <c r="H21" s="10"/>
       <c r="I21" s="12"/>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="8">
         <v>21</v>
       </c>
@@ -2129,15 +1507,15 @@
         <v>0.8</v>
       </c>
       <c r="F22" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G22" s="8">
-        <v>2.08835</v>
+        <v>2.0883500000000002</v>
       </c>
       <c r="H22" s="10"/>
       <c r="I22" s="12"/>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="8">
         <v>22</v>
       </c>
@@ -2154,15 +1532,15 @@
         <v>0.8</v>
       </c>
       <c r="F23" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G23" s="8">
-        <v>2.08836</v>
+        <v>2.0883600000000002</v>
       </c>
       <c r="H23" s="10"/>
       <c r="I23" s="12"/>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="8">
         <v>23</v>
       </c>
@@ -2179,7 +1557,7 @@
         <v>0.8</v>
       </c>
       <c r="F24" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G24" s="8">
         <v>2.08839</v>
@@ -2187,7 +1565,7 @@
       <c r="H24" s="10"/>
       <c r="I24" s="12"/>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="8">
         <v>24</v>
       </c>
@@ -2204,15 +1582,15 @@
         <v>0.8</v>
       </c>
       <c r="F25" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G25" s="8">
-        <v>2.08841</v>
+        <v>2.0884100000000001</v>
       </c>
       <c r="H25" s="10"/>
       <c r="I25" s="12"/>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="8">
         <v>25</v>
       </c>
@@ -2229,15 +1607,15 @@
         <v>0.8</v>
       </c>
       <c r="F26" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G26" s="8">
-        <v>2.08852</v>
+        <v>2.0885199999999999</v>
       </c>
       <c r="H26" s="10"/>
       <c r="I26" s="12"/>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="8">
         <v>26</v>
       </c>
@@ -2254,15 +1632,15 @@
         <v>0.4</v>
       </c>
       <c r="F27" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G27" s="8">
-        <v>2.08895</v>
+        <v>2.0889500000000001</v>
       </c>
       <c r="H27" s="10"/>
       <c r="I27" s="12"/>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="8">
         <v>27</v>
       </c>
@@ -2279,15 +1657,15 @@
         <v>0.8</v>
       </c>
       <c r="F28" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G28" s="8">
-        <v>2.08814</v>
+        <v>2.0881400000000001</v>
       </c>
       <c r="H28" s="10"/>
       <c r="I28" s="12"/>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="8">
         <v>28</v>
       </c>
@@ -2304,15 +1682,15 @@
         <v>0.8</v>
       </c>
       <c r="F29" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G29" s="8">
-        <v>2.08703</v>
+        <v>2.0870299999999999</v>
       </c>
       <c r="H29" s="10"/>
       <c r="I29" s="12"/>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="8">
         <v>29</v>
       </c>
@@ -2329,15 +1707,15 @@
         <v>0.8</v>
       </c>
       <c r="F30" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G30" s="8">
-        <v>2.10099</v>
+        <v>2.1009899999999999</v>
       </c>
       <c r="H30" s="10"/>
       <c r="I30" s="12"/>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="8">
         <v>30</v>
       </c>
@@ -2354,15 +1732,15 @@
         <v>1.2</v>
       </c>
       <c r="F31" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G31" s="8">
-        <v>2.10097</v>
+        <v>2.1009699999999998</v>
       </c>
       <c r="H31" s="10"/>
       <c r="I31" s="12"/>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="8">
         <v>31</v>
       </c>
@@ -2379,15 +1757,15 @@
         <v>0.4</v>
       </c>
       <c r="F32" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G32" s="8">
-        <v>2.10112</v>
+        <v>2.1011199999999999</v>
       </c>
       <c r="H32" s="10"/>
       <c r="I32" s="12"/>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="8">
         <v>32</v>
       </c>
@@ -2404,15 +1782,15 @@
         <v>1.2</v>
       </c>
       <c r="F33" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G33" s="8">
-        <v>2.10098</v>
+        <v>2.1009799999999998</v>
       </c>
       <c r="H33" s="10"/>
       <c r="I33" s="12"/>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="8">
         <v>33</v>
       </c>
@@ -2429,7 +1807,7 @@
         <v>1.2</v>
       </c>
       <c r="F34" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G34" s="8">
         <v>2.101</v>
@@ -2437,7 +1815,7 @@
       <c r="H34" s="10"/>
       <c r="I34" s="12"/>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="8">
         <v>34</v>
       </c>
@@ -2454,15 +1832,15 @@
         <v>1.2</v>
       </c>
       <c r="F35" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G35" s="8">
-        <v>2.10102</v>
+        <v>2.1010200000000001</v>
       </c>
       <c r="H35" s="10"/>
       <c r="I35" s="12"/>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="8">
         <v>35</v>
       </c>
@@ -2479,15 +1857,15 @@
         <v>1.2</v>
       </c>
       <c r="F36" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G36" s="8">
-        <v>2.10103</v>
+        <v>2.1010300000000002</v>
       </c>
       <c r="H36" s="10"/>
       <c r="I36" s="12"/>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="8">
         <v>36</v>
       </c>
@@ -2504,15 +1882,15 @@
         <v>0.4</v>
       </c>
       <c r="F37" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G37" s="8">
-        <v>2.10116</v>
+        <v>2.1011600000000001</v>
       </c>
       <c r="H37" s="10"/>
       <c r="I37" s="12"/>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="8">
         <v>37</v>
       </c>
@@ -2529,15 +1907,15 @@
         <v>1</v>
       </c>
       <c r="F38" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G38" s="8">
-        <v>2.10105</v>
+        <v>2.1010499999999999</v>
       </c>
       <c r="H38" s="10"/>
       <c r="I38" s="12"/>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="8">
         <v>38</v>
       </c>
@@ -2554,15 +1932,15 @@
         <v>0.4</v>
       </c>
       <c r="F39" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G39" s="8">
-        <v>2.10123</v>
+        <v>2.1012300000000002</v>
       </c>
       <c r="H39" s="10"/>
       <c r="I39" s="12"/>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="8">
         <v>39</v>
       </c>
@@ -2579,15 +1957,15 @@
         <v>0.4</v>
       </c>
       <c r="F40" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G40" s="8">
-        <v>2.10251</v>
+        <v>2.1025100000000001</v>
       </c>
       <c r="H40" s="10"/>
       <c r="I40" s="12"/>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="8">
         <v>40</v>
       </c>
@@ -2598,21 +1976,21 @@
         <v>43</v>
       </c>
       <c r="D41" s="8">
-        <v>546.2</v>
+        <v>546.20000000000005</v>
       </c>
       <c r="E41" s="8">
         <v>1</v>
       </c>
       <c r="F41" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G41" s="8">
-        <v>2.10106</v>
+        <v>2.1010599999999999</v>
       </c>
       <c r="H41" s="10"/>
       <c r="I41" s="12"/>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="8">
         <v>41</v>
       </c>
@@ -2629,15 +2007,15 @@
         <v>0.4</v>
       </c>
       <c r="F42" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G42" s="8">
-        <v>2.10115</v>
+        <v>2.1011500000000001</v>
       </c>
       <c r="H42" s="10"/>
       <c r="I42" s="12"/>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="8">
         <v>42</v>
       </c>
@@ -2654,7 +2032,7 @@
         <v>1</v>
       </c>
       <c r="F43" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G43" s="8">
         <v>2.10107</v>
@@ -2662,7 +2040,7 @@
       <c r="H43" s="10"/>
       <c r="I43" s="12"/>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="8">
         <v>43</v>
       </c>
@@ -2679,15 +2057,15 @@
         <v>0.4</v>
       </c>
       <c r="F44" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G44" s="8">
-        <v>2.10113</v>
+        <v>2.1011299999999999</v>
       </c>
       <c r="H44" s="10"/>
       <c r="I44" s="12"/>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="8">
         <v>44</v>
       </c>
@@ -2704,15 +2082,15 @@
         <v>0.4</v>
       </c>
       <c r="F45" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G45" s="8">
-        <v>2.1011</v>
+        <v>2.1011000000000002</v>
       </c>
       <c r="H45" s="10"/>
       <c r="I45" s="12"/>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="8">
         <v>45</v>
       </c>
@@ -2729,15 +2107,15 @@
         <v>1</v>
       </c>
       <c r="F46" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G46" s="8">
-        <v>2.10109</v>
+        <v>2.1010900000000001</v>
       </c>
       <c r="H46" s="10"/>
       <c r="I46" s="12"/>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="8">
         <v>46</v>
       </c>
@@ -2754,15 +2132,15 @@
         <v>1</v>
       </c>
       <c r="F47" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G47" s="8">
-        <v>2.10112</v>
+        <v>2.1011199999999999</v>
       </c>
       <c r="H47" s="10"/>
       <c r="I47" s="12"/>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="8">
         <v>47</v>
       </c>
@@ -2779,7 +2157,7 @@
         <v>0.6</v>
       </c>
       <c r="F48" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G48" s="8">
         <v>2.1012</v>
@@ -2787,7 +2165,7 @@
       <c r="H48" s="10"/>
       <c r="I48" s="12"/>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="8">
         <v>48</v>
       </c>
@@ -2798,13 +2176,13 @@
         <v>65</v>
       </c>
       <c r="D49" s="8">
-        <v>614.33</v>
+        <v>614.33000000000004</v>
       </c>
       <c r="E49" s="8">
         <v>0.6</v>
       </c>
       <c r="F49" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G49" s="8">
         <v>2.10121</v>
@@ -2812,7 +2190,7 @@
       <c r="H49" s="10"/>
       <c r="I49" s="12"/>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="8">
         <v>49</v>
       </c>
@@ -2829,7 +2207,7 @@
         <v>0.6</v>
       </c>
       <c r="F50" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G50" s="8">
         <v>2.10121</v>
@@ -2837,7 +2215,7 @@
       <c r="H50" s="10"/>
       <c r="I50" s="12"/>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="8">
         <v>50</v>
       </c>
@@ -2854,15 +2232,15 @@
         <v>0.6</v>
       </c>
       <c r="F51" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G51" s="8">
-        <v>2.10123</v>
+        <v>2.1012300000000002</v>
       </c>
       <c r="H51" s="10"/>
       <c r="I51" s="12"/>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="8">
         <v>51</v>
       </c>
@@ -2879,15 +2257,15 @@
         <v>0.6</v>
       </c>
       <c r="F52" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G52" s="8">
-        <v>2.10125</v>
+        <v>2.1012499999999998</v>
       </c>
       <c r="H52" s="10"/>
       <c r="I52" s="12"/>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="8">
         <v>52</v>
       </c>
@@ -2904,15 +2282,15 @@
         <v>0.6</v>
       </c>
       <c r="F53" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G53" s="8">
-        <v>2.10126</v>
+        <v>2.1012599999999999</v>
       </c>
       <c r="H53" s="10"/>
       <c r="I53" s="12"/>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="8">
         <v>53</v>
       </c>
@@ -2929,7 +2307,7 @@
         <v>0.4</v>
       </c>
       <c r="F54" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G54" s="8">
         <v>2.10128</v>
@@ -2937,7 +2315,7 @@
       <c r="H54" s="10"/>
       <c r="I54" s="12"/>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="8">
         <v>54</v>
       </c>
@@ -2954,7 +2332,7 @@
         <v>0.6</v>
       </c>
       <c r="F55" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G55" s="8">
         <v>2.10127</v>
@@ -2962,7 +2340,7 @@
       <c r="H55" s="10"/>
       <c r="I55" s="12"/>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="8">
         <v>55</v>
       </c>
@@ -2979,15 +2357,15 @@
         <v>0.4</v>
       </c>
       <c r="F56" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G56" s="8">
-        <v>2.1013</v>
+        <v>2.1013000000000002</v>
       </c>
       <c r="H56" s="10"/>
       <c r="I56" s="12"/>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="8">
         <v>56</v>
       </c>
@@ -3004,15 +2382,15 @@
         <v>0.4</v>
       </c>
       <c r="F57" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G57" s="8">
-        <v>2.10137</v>
+        <v>2.1013700000000002</v>
       </c>
       <c r="H57" s="10"/>
       <c r="I57" s="12"/>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="8">
         <v>57</v>
       </c>
@@ -3029,15 +2407,15 @@
         <v>0.4</v>
       </c>
       <c r="F58" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G58" s="8">
-        <v>2.1014</v>
+        <v>2.1013999999999999</v>
       </c>
       <c r="H58" s="10"/>
       <c r="I58" s="12"/>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="8">
         <v>58</v>
       </c>
@@ -3054,7 +2432,7 @@
         <v>0.4</v>
       </c>
       <c r="F59" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G59" s="8">
         <v>2.10141</v>
@@ -3062,7 +2440,7 @@
       <c r="H59" s="10"/>
       <c r="I59" s="12"/>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="8">
         <v>59</v>
       </c>
@@ -3079,7 +2457,7 @@
         <v>0.4</v>
       </c>
       <c r="F60" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G60" s="8">
         <v>2.10161</v>
@@ -3087,7 +2465,7 @@
       <c r="H60" s="10"/>
       <c r="I60" s="12"/>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="8">
         <v>60</v>
       </c>
@@ -3104,15 +2482,15 @@
         <v>0.6</v>
       </c>
       <c r="F61" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G61" s="8">
-        <v>2.10144</v>
+        <v>2.1014400000000002</v>
       </c>
       <c r="H61" s="10"/>
       <c r="I61" s="12"/>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="8">
         <v>61</v>
       </c>
@@ -3129,15 +2507,15 @@
         <v>0.4</v>
       </c>
       <c r="F62" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G62" s="8">
-        <v>2.10158</v>
+        <v>2.1015799999999998</v>
       </c>
       <c r="H62" s="10"/>
       <c r="I62" s="12"/>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="8">
         <v>62</v>
       </c>
@@ -3154,7 +2532,7 @@
         <v>0.6</v>
       </c>
       <c r="F63" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G63" s="8">
         <v>2.10155</v>
@@ -3162,7 +2540,7 @@
       <c r="H63" s="10"/>
       <c r="I63" s="12"/>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="8">
         <v>63</v>
       </c>
@@ -3179,15 +2557,15 @@
         <v>0.6</v>
       </c>
       <c r="F64" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G64" s="8">
-        <v>2.10174</v>
+        <v>2.1017399999999999</v>
       </c>
       <c r="H64" s="10"/>
       <c r="I64" s="12"/>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="8">
         <v>64</v>
       </c>
@@ -3204,15 +2582,15 @@
         <v>0.8</v>
       </c>
       <c r="F65" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G65" s="8">
-        <v>2.10131</v>
+        <v>2.1013099999999998</v>
       </c>
       <c r="H65" s="10"/>
       <c r="I65" s="12"/>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="8">
         <v>65</v>
       </c>
@@ -3229,15 +2607,15 @@
         <v>0.8</v>
       </c>
       <c r="F66" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G66" s="8">
-        <v>2.10137</v>
+        <v>2.1013700000000002</v>
       </c>
       <c r="H66" s="10"/>
       <c r="I66" s="12"/>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="8">
         <v>66</v>
       </c>
@@ -3248,21 +2626,21 @@
         <v>56</v>
       </c>
       <c r="D67" s="8">
-        <v>643.3</v>
+        <v>643.29999999999995</v>
       </c>
       <c r="E67" s="8">
         <v>0.8</v>
       </c>
       <c r="F67" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G67" s="8">
-        <v>2.10146</v>
+        <v>2.1014599999999999</v>
       </c>
       <c r="H67" s="10"/>
       <c r="I67" s="12"/>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="8">
         <v>67</v>
       </c>
@@ -3279,7 +2657,7 @@
         <v>0.8</v>
       </c>
       <c r="F68" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G68" s="8">
         <v>2.10175</v>
@@ -3287,7 +2665,7 @@
       <c r="H68" s="10"/>
       <c r="I68" s="12"/>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="8">
         <v>68</v>
       </c>
@@ -3304,15 +2682,15 @@
         <v>0.6</v>
       </c>
       <c r="F69" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G69" s="8">
-        <v>2.10254</v>
+        <v>2.1025399999999999</v>
       </c>
       <c r="H69" s="10"/>
       <c r="I69" s="12"/>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="8">
         <v>69</v>
       </c>
@@ -3329,219 +2707,218 @@
         <v>0.7</v>
       </c>
       <c r="F70" s="8">
-        <v>0.0004</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="G70" s="8">
-        <v>2.0881</v>
+        <v>2.0880999999999998</v>
       </c>
       <c r="H70" s="10"/>
       <c r="I70" s="12"/>
     </row>
-    <row r="71" spans="8:8">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H71" s="13"/>
     </row>
-    <row r="72" spans="8:8">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H72" s="13"/>
     </row>
-    <row r="73" spans="8:8">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H73" s="13"/>
     </row>
-    <row r="74" spans="8:8">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H74" s="13"/>
     </row>
-    <row r="75" spans="8:8">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H75" s="13"/>
     </row>
-    <row r="76" spans="8:8">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H76" s="13"/>
     </row>
-    <row r="77" spans="8:8">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H77" s="13"/>
     </row>
-    <row r="78" spans="8:8">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H78" s="13"/>
     </row>
-    <row r="79" spans="8:8">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H79" s="13"/>
     </row>
-    <row r="80" spans="8:8">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H80" s="13"/>
     </row>
-    <row r="81" spans="8:8">
+    <row r="81" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H81" s="13"/>
     </row>
-    <row r="82" spans="8:8">
+    <row r="82" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H82" s="13"/>
     </row>
-    <row r="83" spans="8:8">
+    <row r="83" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H83" s="13"/>
     </row>
-    <row r="84" spans="8:8">
+    <row r="84" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H84" s="13"/>
     </row>
-    <row r="85" spans="8:8">
+    <row r="85" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H85" s="13"/>
     </row>
-    <row r="86" spans="8:8">
+    <row r="86" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H86" s="13"/>
     </row>
-    <row r="87" spans="8:8">
+    <row r="87" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H87" s="13"/>
     </row>
-    <row r="88" spans="8:8">
+    <row r="88" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H88" s="13"/>
     </row>
-    <row r="89" spans="8:8">
+    <row r="89" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H89" s="13"/>
     </row>
-    <row r="90" spans="8:8">
+    <row r="90" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H90" s="13"/>
     </row>
-    <row r="91" spans="8:8">
+    <row r="91" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H91" s="13"/>
     </row>
-    <row r="92" spans="8:8">
+    <row r="92" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H92" s="13"/>
     </row>
-    <row r="93" spans="8:8">
+    <row r="93" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H93" s="13"/>
     </row>
-    <row r="94" spans="8:8">
+    <row r="94" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H94" s="13"/>
     </row>
-    <row r="95" spans="8:8">
+    <row r="95" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H95" s="13"/>
     </row>
-    <row r="96" spans="8:8">
+    <row r="96" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H96" s="13"/>
     </row>
-    <row r="97" spans="8:8">
+    <row r="97" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H97" s="13"/>
     </row>
-    <row r="98" spans="8:8">
+    <row r="98" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H98" s="13"/>
     </row>
-    <row r="99" spans="8:8">
+    <row r="99" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H99" s="13"/>
     </row>
-    <row r="100" spans="8:8">
+    <row r="100" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H100" s="13"/>
     </row>
-    <row r="101" spans="8:8">
+    <row r="101" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H101" s="13"/>
     </row>
-    <row r="102" spans="8:8">
+    <row r="102" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H102" s="13"/>
     </row>
-    <row r="103" spans="8:8">
+    <row r="103" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H103" s="13"/>
     </row>
-    <row r="104" spans="8:8">
+    <row r="104" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H104" s="13"/>
     </row>
-    <row r="105" spans="8:8">
+    <row r="105" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H105" s="13"/>
     </row>
-    <row r="106" spans="8:8">
+    <row r="106" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H106" s="13"/>
     </row>
-    <row r="107" spans="8:8">
+    <row r="107" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H107" s="13"/>
     </row>
-    <row r="108" spans="8:8">
+    <row r="108" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H108" s="13"/>
     </row>
-    <row r="109" spans="8:8">
+    <row r="109" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H109" s="13"/>
     </row>
-    <row r="110" spans="8:8">
+    <row r="110" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H110" s="13"/>
     </row>
-    <row r="111" spans="8:8">
+    <row r="111" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H111" s="13"/>
     </row>
-    <row r="112" spans="8:8">
+    <row r="112" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H112" s="13"/>
     </row>
-    <row r="113" spans="8:8">
+    <row r="113" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H113" s="13"/>
     </row>
-    <row r="114" spans="8:8">
+    <row r="114" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H114" s="13"/>
     </row>
-    <row r="115" spans="8:8">
+    <row r="115" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H115" s="13"/>
     </row>
-    <row r="116" spans="8:8">
+    <row r="116" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H116" s="13"/>
     </row>
-    <row r="117" spans="8:8">
+    <row r="117" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H117" s="13"/>
     </row>
-    <row r="118" spans="8:8">
+    <row r="118" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H118" s="13"/>
     </row>
-    <row r="119" spans="8:8">
+    <row r="119" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H119" s="13"/>
     </row>
-    <row r="120" spans="8:8">
+    <row r="120" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H120" s="13"/>
     </row>
-    <row r="121" spans="8:8">
+    <row r="121" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H121" s="13"/>
     </row>
-    <row r="122" spans="8:8">
+    <row r="122" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H122" s="13"/>
     </row>
-    <row r="123" spans="8:8">
+    <row r="123" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H123" s="13"/>
     </row>
-    <row r="124" spans="8:8">
+    <row r="124" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H124" s="13"/>
     </row>
-    <row r="125" spans="8:8">
+    <row r="125" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H125" s="13"/>
     </row>
-    <row r="126" spans="8:8">
+    <row r="126" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H126" s="13"/>
     </row>
-    <row r="127" spans="8:8">
+    <row r="127" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H127" s="13"/>
     </row>
-    <row r="128" spans="8:8">
+    <row r="128" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H128" s="13"/>
     </row>
-    <row r="129" spans="8:8">
+    <row r="129" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H129" s="13"/>
     </row>
-    <row r="130" spans="8:8">
+    <row r="130" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H130" s="13"/>
     </row>
-    <row r="131" spans="8:8">
+    <row r="131" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H131" s="13"/>
     </row>
-    <row r="132" spans="8:8">
+    <row r="132" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H132" s="13"/>
     </row>
-    <row r="133" spans="8:8">
+    <row r="133" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H133" s="13"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H134"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="16.3333333333333" customWidth="1"/>
+    <col min="2" max="2" width="16.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:8">
+    <row r="1" spans="1:8" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
@@ -3563,7 +2940,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -3580,7 +2957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>2</v>
       </c>
@@ -3597,12 +2974,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>3</v>
       </c>
       <c r="B4" s="6">
-        <v>6.306307429</v>
+        <v>6.3063074290000003</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>13</v>
@@ -3614,7 +2991,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>4</v>
       </c>
@@ -3631,12 +3008,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>5</v>
       </c>
       <c r="B6" s="6">
-        <v>4.036036755</v>
+        <v>4.0360367549999996</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>13</v>
@@ -3648,7 +3025,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>6</v>
       </c>
@@ -3665,7 +3042,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>7</v>
       </c>
@@ -3682,7 +3059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>8</v>
       </c>
@@ -3699,7 +3076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>9</v>
       </c>
@@ -3716,7 +3093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>10</v>
       </c>
@@ -3733,12 +3110,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>11</v>
       </c>
       <c r="B12" s="6">
-        <v>30.52252796</v>
+        <v>30.522527960000001</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>13</v>
@@ -3750,7 +3127,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>12</v>
       </c>
@@ -3767,12 +3144,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>13</v>
       </c>
       <c r="B14" s="6">
-        <v>3.3456</v>
+        <v>3.3456000000000001</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>13</v>
@@ -3784,7 +3161,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>14</v>
       </c>
@@ -3801,7 +3178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:8" ht="15" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>15</v>
       </c>
@@ -3818,7 +3195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>16</v>
       </c>
@@ -3835,7 +3212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>17</v>
       </c>
@@ -3852,7 +3229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>18</v>
       </c>
@@ -3869,7 +3246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>19</v>
       </c>
@@ -3886,7 +3263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>20</v>
       </c>
@@ -3903,7 +3280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>21</v>
       </c>
@@ -3920,7 +3297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>22</v>
       </c>
@@ -3937,7 +3314,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>23</v>
       </c>
@@ -3954,7 +3331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>24</v>
       </c>
@@ -3971,7 +3348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>25</v>
       </c>
@@ -3988,7 +3365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>26</v>
       </c>
@@ -4005,12 +3382,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>27</v>
       </c>
       <c r="B28" s="6">
-        <v>3.3456</v>
+        <v>3.3456000000000001</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>13</v>
@@ -4022,7 +3399,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>28</v>
       </c>
@@ -4039,12 +3416,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>29</v>
       </c>
       <c r="B30" s="6">
-        <v>6.306307429</v>
+        <v>6.3063074290000003</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>13</v>
@@ -4056,12 +3433,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>30</v>
       </c>
       <c r="B31" s="6">
-        <v>6.306307429</v>
+        <v>6.3063074290000003</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>13</v>
@@ -4073,7 +3450,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>31</v>
       </c>
@@ -4090,7 +3467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>32</v>
       </c>
@@ -4107,12 +3484,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>33</v>
       </c>
       <c r="B34" s="6">
-        <v>3.3456</v>
+        <v>3.3456000000000001</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>13</v>
@@ -4124,7 +3501,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>34</v>
       </c>
@@ -4141,7 +3518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>35</v>
       </c>
@@ -4158,7 +3535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>36</v>
       </c>
@@ -4175,7 +3552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>37</v>
       </c>
@@ -4192,7 +3569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>38</v>
       </c>
@@ -4209,12 +3586,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>39</v>
       </c>
       <c r="B40" s="6">
-        <v>3.3456</v>
+        <v>3.3456000000000001</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>13</v>
@@ -4226,12 +3603,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>40</v>
       </c>
       <c r="B41" s="6">
-        <v>3.3456</v>
+        <v>3.3456000000000001</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>13</v>
@@ -4243,7 +3620,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>41</v>
       </c>
@@ -4260,12 +3637,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>42</v>
       </c>
       <c r="B43" s="6">
-        <v>4.036036755</v>
+        <v>4.0360367549999996</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>13</v>
@@ -4277,7 +3654,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>43</v>
       </c>
@@ -4294,7 +3671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>44</v>
       </c>
@@ -4311,7 +3688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>45</v>
       </c>
@@ -4328,12 +3705,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>46</v>
       </c>
       <c r="B47" s="6">
-        <v>3.3456</v>
+        <v>3.3456000000000001</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>13</v>
@@ -4345,12 +3722,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>47</v>
       </c>
       <c r="B48" s="6">
-        <v>3.3456</v>
+        <v>3.3456000000000001</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>13</v>
@@ -4362,12 +3739,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>48</v>
       </c>
       <c r="B49" s="6">
-        <v>3.3456</v>
+        <v>3.3456000000000001</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>13</v>
@@ -4379,7 +3756,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>49</v>
       </c>
@@ -4396,7 +3773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>50</v>
       </c>
@@ -4413,7 +3790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>51</v>
       </c>
@@ -4430,12 +3807,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>52</v>
       </c>
       <c r="B53" s="6">
-        <v>4.036036755</v>
+        <v>4.0360367549999996</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>13</v>
@@ -4447,7 +3824,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>53</v>
       </c>
@@ -4464,12 +3841,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>54</v>
       </c>
       <c r="B55" s="6">
-        <v>228.2694063</v>
+        <v>228.26940630000001</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>13</v>
@@ -4481,7 +3858,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>55</v>
       </c>
@@ -4498,7 +3875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>56</v>
       </c>
@@ -4515,7 +3892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>57</v>
       </c>
@@ -4532,7 +3909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>58</v>
       </c>
@@ -4549,7 +3926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>59</v>
       </c>
@@ -4566,7 +3943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>60</v>
       </c>
@@ -4583,12 +3960,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>61</v>
       </c>
       <c r="B62" s="6">
-        <v>6.306307429</v>
+        <v>6.3063074290000003</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>13</v>
@@ -4600,7 +3977,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>62</v>
       </c>
@@ -4617,7 +3994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>63</v>
       </c>
@@ -4634,7 +4011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>64</v>
       </c>
@@ -4651,7 +4028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>65</v>
       </c>
@@ -4668,7 +4045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>66</v>
       </c>
@@ -4685,7 +4062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>67</v>
       </c>
@@ -4702,7 +4079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>68</v>
       </c>
@@ -4719,7 +4096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>69</v>
       </c>
@@ -4736,425 +4113,421 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4">
+    <row r="71" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A71" s="7"/>
       <c r="B71" s="7"/>
       <c r="C71" s="7"/>
       <c r="D71" s="7"/>
     </row>
-    <row r="72" spans="1:4">
+    <row r="72" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A72" s="7"/>
       <c r="B72" s="7"/>
       <c r="C72" s="7"/>
       <c r="D72" s="7"/>
     </row>
-    <row r="73" spans="1:4">
+    <row r="73" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A73" s="7"/>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
       <c r="D73" s="7"/>
     </row>
-    <row r="74" spans="1:4">
+    <row r="74" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A74" s="7"/>
       <c r="B74" s="7"/>
       <c r="C74" s="7"/>
       <c r="D74" s="7"/>
     </row>
-    <row r="75" spans="1:4">
+    <row r="75" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A75" s="7"/>
       <c r="B75" s="7"/>
       <c r="C75" s="7"/>
       <c r="D75" s="7"/>
     </row>
-    <row r="76" spans="1:4">
+    <row r="76" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A76" s="7"/>
       <c r="B76" s="7"/>
       <c r="C76" s="7"/>
       <c r="D76" s="7"/>
     </row>
-    <row r="77" spans="1:4">
+    <row r="77" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A77" s="7"/>
       <c r="B77" s="7"/>
       <c r="C77" s="7"/>
       <c r="D77" s="7"/>
     </row>
-    <row r="78" spans="1:4">
+    <row r="78" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
       <c r="D78" s="7"/>
     </row>
-    <row r="79" spans="1:4">
+    <row r="79" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A79" s="7"/>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
       <c r="D79" s="7"/>
     </row>
-    <row r="80" spans="1:4">
+    <row r="80" spans="1:5" ht="15" x14ac:dyDescent="0.25">
       <c r="A80" s="7"/>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
       <c r="D80" s="7"/>
     </row>
-    <row r="81" spans="1:4">
+    <row r="81" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A81" s="7"/>
       <c r="B81" s="7"/>
       <c r="C81" s="7"/>
       <c r="D81" s="7"/>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
       <c r="D82" s="7"/>
     </row>
-    <row r="83" spans="1:4">
+    <row r="83" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
       <c r="C83" s="7"/>
       <c r="D83" s="7"/>
     </row>
-    <row r="84" spans="1:4">
+    <row r="84" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
       <c r="D84" s="7"/>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A85" s="7"/>
       <c r="B85" s="7"/>
       <c r="C85" s="7"/>
       <c r="D85" s="7"/>
     </row>
-    <row r="86" spans="1:4">
+    <row r="86" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A86" s="7"/>
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
       <c r="D86" s="7"/>
     </row>
-    <row r="87" spans="1:4">
+    <row r="87" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A87" s="7"/>
       <c r="B87" s="7"/>
       <c r="C87" s="7"/>
       <c r="D87" s="7"/>
     </row>
-    <row r="88" spans="1:4">
+    <row r="88" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A88" s="7"/>
       <c r="B88" s="7"/>
       <c r="C88" s="7"/>
       <c r="D88" s="7"/>
     </row>
-    <row r="89" spans="1:4">
+    <row r="89" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A89" s="7"/>
       <c r="B89" s="7"/>
       <c r="C89" s="7"/>
       <c r="D89" s="7"/>
     </row>
-    <row r="90" spans="1:4">
+    <row r="90" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="7"/>
       <c r="D90" s="7"/>
     </row>
-    <row r="91" spans="1:4">
+    <row r="91" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A91" s="7"/>
       <c r="B91" s="7"/>
       <c r="C91" s="7"/>
       <c r="D91" s="7"/>
     </row>
-    <row r="92" spans="1:4">
+    <row r="92" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A92" s="7"/>
       <c r="B92" s="7"/>
       <c r="C92" s="7"/>
       <c r="D92" s="7"/>
     </row>
-    <row r="93" spans="1:4">
+    <row r="93" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A93" s="7"/>
       <c r="B93" s="7"/>
       <c r="C93" s="7"/>
       <c r="D93" s="7"/>
     </row>
-    <row r="94" spans="1:4">
+    <row r="94" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A94" s="7"/>
       <c r="B94" s="7"/>
       <c r="C94" s="7"/>
       <c r="D94" s="7"/>
     </row>
-    <row r="95" spans="1:4">
+    <row r="95" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A95" s="7"/>
       <c r="B95" s="7"/>
       <c r="C95" s="7"/>
       <c r="D95" s="7"/>
     </row>
-    <row r="96" spans="1:4">
+    <row r="96" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A96" s="7"/>
       <c r="B96" s="7"/>
       <c r="C96" s="7"/>
       <c r="D96" s="7"/>
     </row>
-    <row r="97" spans="1:4">
+    <row r="97" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A97" s="7"/>
       <c r="B97" s="7"/>
       <c r="C97" s="7"/>
       <c r="D97" s="7"/>
     </row>
-    <row r="98" spans="1:4">
+    <row r="98" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A98" s="7"/>
       <c r="B98" s="7"/>
       <c r="C98" s="7"/>
       <c r="D98" s="7"/>
     </row>
-    <row r="99" spans="1:4">
+    <row r="99" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A99" s="7"/>
       <c r="B99" s="7"/>
       <c r="C99" s="7"/>
       <c r="D99" s="7"/>
     </row>
-    <row r="100" spans="1:4">
+    <row r="100" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A100" s="7"/>
       <c r="B100" s="7"/>
       <c r="C100" s="7"/>
       <c r="D100" s="7"/>
     </row>
-    <row r="101" spans="1:4">
+    <row r="101" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A101" s="7"/>
       <c r="B101" s="7"/>
-      <c r="C101"/>
       <c r="D101" s="7"/>
     </row>
-    <row r="102" spans="1:4">
+    <row r="102" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A102" s="7"/>
       <c r="B102" s="7"/>
-      <c r="C102"/>
       <c r="D102" s="7"/>
     </row>
-    <row r="103" spans="1:4">
+    <row r="103" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A103" s="7"/>
       <c r="B103" s="7"/>
       <c r="C103" s="7"/>
       <c r="D103" s="7"/>
     </row>
-    <row r="104" spans="1:4">
+    <row r="104" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A104" s="7"/>
       <c r="B104" s="7"/>
       <c r="C104" s="7"/>
       <c r="D104" s="7"/>
     </row>
-    <row r="105" spans="1:4">
+    <row r="105" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A105" s="7"/>
       <c r="B105" s="7"/>
       <c r="C105" s="7"/>
       <c r="D105" s="7"/>
     </row>
-    <row r="106" spans="1:4">
+    <row r="106" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A106" s="7"/>
       <c r="B106" s="7"/>
       <c r="C106" s="7"/>
       <c r="D106" s="7"/>
     </row>
-    <row r="107" spans="1:4">
+    <row r="107" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A107" s="7"/>
       <c r="B107" s="7"/>
       <c r="C107" s="7"/>
       <c r="D107" s="7"/>
     </row>
-    <row r="108" spans="1:4">
+    <row r="108" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A108" s="7"/>
       <c r="B108" s="7"/>
       <c r="C108" s="7"/>
       <c r="D108" s="7"/>
     </row>
-    <row r="109" spans="1:4">
+    <row r="109" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A109" s="7"/>
       <c r="B109" s="7"/>
       <c r="C109" s="7"/>
       <c r="D109" s="7"/>
     </row>
-    <row r="110" spans="1:4">
+    <row r="110" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A110" s="7"/>
       <c r="B110" s="7"/>
       <c r="C110" s="7"/>
       <c r="D110" s="7"/>
     </row>
-    <row r="111" spans="1:4">
+    <row r="111" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A111" s="7"/>
       <c r="B111" s="7"/>
       <c r="C111" s="7"/>
       <c r="D111" s="7"/>
     </row>
-    <row r="112" spans="1:4">
+    <row r="112" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A112" s="7"/>
       <c r="B112" s="7"/>
       <c r="C112" s="7"/>
       <c r="D112" s="7"/>
     </row>
-    <row r="113" spans="1:4">
+    <row r="113" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A113" s="7"/>
       <c r="B113" s="7"/>
       <c r="C113" s="7"/>
       <c r="D113" s="7"/>
     </row>
-    <row r="114" spans="1:4">
+    <row r="114" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A114" s="7"/>
       <c r="B114" s="7"/>
       <c r="C114" s="7"/>
       <c r="D114" s="7"/>
     </row>
-    <row r="115" spans="1:4">
+    <row r="115" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A115" s="7"/>
       <c r="B115" s="7"/>
       <c r="C115" s="7"/>
       <c r="D115" s="7"/>
     </row>
-    <row r="116" spans="1:4">
+    <row r="116" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A116" s="7"/>
       <c r="B116" s="7"/>
       <c r="C116" s="7"/>
       <c r="D116" s="7"/>
     </row>
-    <row r="117" spans="1:4">
+    <row r="117" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A117" s="7"/>
       <c r="B117" s="7"/>
       <c r="C117" s="7"/>
       <c r="D117" s="7"/>
     </row>
-    <row r="118" spans="1:4">
+    <row r="118" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A118" s="7"/>
       <c r="B118" s="7"/>
       <c r="C118" s="7"/>
       <c r="D118" s="7"/>
     </row>
-    <row r="119" spans="1:4">
+    <row r="119" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A119" s="7"/>
       <c r="B119" s="7"/>
       <c r="C119" s="7"/>
       <c r="D119" s="7"/>
     </row>
-    <row r="120" spans="1:4">
+    <row r="120" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A120" s="7"/>
       <c r="B120" s="7"/>
       <c r="C120" s="7"/>
       <c r="D120" s="7"/>
     </row>
-    <row r="121" spans="1:4">
+    <row r="121" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A121" s="7"/>
       <c r="B121" s="7"/>
       <c r="C121" s="7"/>
       <c r="D121" s="7"/>
     </row>
-    <row r="122" spans="1:4">
+    <row r="122" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A122" s="7"/>
       <c r="B122" s="7"/>
       <c r="C122" s="7"/>
       <c r="D122" s="7"/>
     </row>
-    <row r="123" spans="1:4">
+    <row r="123" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A123" s="7"/>
       <c r="B123" s="7"/>
       <c r="C123" s="7"/>
       <c r="D123" s="7"/>
     </row>
-    <row r="124" spans="1:4">
+    <row r="124" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A124" s="7"/>
       <c r="B124" s="7"/>
       <c r="C124" s="7"/>
       <c r="D124" s="7"/>
     </row>
-    <row r="125" spans="1:4">
+    <row r="125" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A125" s="7"/>
       <c r="B125" s="7"/>
       <c r="C125" s="7"/>
       <c r="D125" s="7"/>
     </row>
-    <row r="126" spans="1:4">
+    <row r="126" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A126" s="7"/>
       <c r="B126" s="7"/>
       <c r="C126" s="7"/>
       <c r="D126" s="7"/>
     </row>
-    <row r="127" spans="1:4">
+    <row r="127" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A127" s="7"/>
       <c r="B127" s="7"/>
       <c r="C127" s="7"/>
       <c r="D127" s="7"/>
     </row>
-    <row r="128" spans="1:4">
+    <row r="128" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A128" s="7"/>
       <c r="B128" s="7"/>
       <c r="C128" s="7"/>
       <c r="D128" s="7"/>
     </row>
-    <row r="129" spans="1:4">
+    <row r="129" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A129" s="7"/>
       <c r="B129" s="7"/>
       <c r="C129" s="7"/>
       <c r="D129" s="7"/>
     </row>
-    <row r="130" spans="1:4">
+    <row r="130" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A130" s="7"/>
       <c r="B130" s="7"/>
       <c r="C130" s="7"/>
       <c r="D130" s="7"/>
     </row>
-    <row r="131" spans="1:4">
+    <row r="131" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A131" s="7"/>
       <c r="B131" s="7"/>
       <c r="C131" s="7"/>
       <c r="D131" s="7"/>
     </row>
-    <row r="132" spans="1:4">
+    <row r="132" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A132" s="7"/>
       <c r="B132" s="7"/>
       <c r="C132" s="7"/>
       <c r="D132" s="7"/>
     </row>
-    <row r="133" spans="1:4">
+    <row r="133" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A133" s="7"/>
       <c r="B133" s="7"/>
       <c r="C133" s="7"/>
       <c r="D133" s="7"/>
     </row>
-    <row r="134" spans="1:4">
+    <row r="134" spans="1:4" ht="15" x14ac:dyDescent="0.25">
       <c r="A134" s="7"/>
       <c r="B134" s="7"/>
       <c r="C134" s="7"/>
       <c r="D134" s="7"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>100</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:O19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
@@ -5201,7 +4574,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>16</v>
       </c>
@@ -5248,7 +4621,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>27</v>
       </c>
@@ -5295,7 +4668,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>30</v>
       </c>
@@ -5342,7 +4715,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>33</v>
       </c>
@@ -5389,7 +4762,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>36</v>
       </c>
@@ -5436,7 +4809,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>39</v>
       </c>
@@ -5483,7 +4856,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>42</v>
       </c>
@@ -5530,7 +4903,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>45</v>
       </c>
@@ -5577,7 +4950,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>48</v>
       </c>
@@ -5624,7 +4997,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>50</v>
       </c>
@@ -5671,7 +5044,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>53</v>
       </c>
@@ -5718,7 +5091,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>57</v>
       </c>
@@ -5765,7 +5138,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>60</v>
       </c>
@@ -5812,7 +5185,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>63</v>
       </c>
@@ -5859,7 +5232,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>66</v>
       </c>
@@ -5906,7 +5279,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:15" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>69</v>
       </c>
@@ -5953,7 +5326,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:15" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>72</v>
       </c>
@@ -6000,7 +5373,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:15" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>76</v>
       </c>
@@ -6048,36 +5421,35 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:P187"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="1">
+        <v>3.7030000000000001E-3</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>47</v>
@@ -6095,13 +5467,13 @@
         <v>15</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+    </row>
+    <row r="2" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>16</v>
       </c>
@@ -6109,16 +5481,16 @@
         <v>27</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>47</v>
@@ -6136,30 +5508,30 @@
         <v>15</v>
       </c>
       <c r="L2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+    </row>
+    <row r="3" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="1">
+        <v>1.7899999999999999E-2</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>47</v>
@@ -6177,13 +5549,13 @@
         <v>15</v>
       </c>
       <c r="L3" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+    </row>
+    <row r="4" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>30</v>
       </c>
@@ -6191,16 +5563,16 @@
         <v>33</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>47</v>
@@ -6218,30 +5590,30 @@
         <v>15</v>
       </c>
       <c r="L4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="M4" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M4" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
+    </row>
+    <row r="5" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>93</v>
+      <c r="C5" s="1">
+        <v>1.4318000000000001E-2</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>47</v>
@@ -6259,31 +5631,31 @@
         <v>15</v>
       </c>
       <c r="L5" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M5" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="M5" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="P5" s="4"/>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>96</v>
+      <c r="C6" s="2">
+        <v>1.5029000000000001E-2</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>47</v>
@@ -6301,13 +5673,13 @@
         <v>15</v>
       </c>
       <c r="L6" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="M6" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M6" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+    </row>
+    <row r="7" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>39</v>
       </c>
@@ -6315,16 +5687,16 @@
         <v>42</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>47</v>
@@ -6342,13 +5714,13 @@
         <v>15</v>
       </c>
       <c r="L7" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M7" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="M7" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+    </row>
+    <row r="8" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>39</v>
       </c>
@@ -6356,16 +5728,16 @@
         <v>45</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>47</v>
@@ -6383,13 +5755,13 @@
         <v>15</v>
       </c>
       <c r="L8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="M8" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M8" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+    </row>
+    <row r="9" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>30</v>
       </c>
@@ -6397,16 +5769,16 @@
         <v>48</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>47</v>
@@ -6424,13 +5796,13 @@
         <v>15</v>
       </c>
       <c r="L9" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M9" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="M9" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+    </row>
+    <row r="10" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>15</v>
       </c>
@@ -6438,16 +5810,16 @@
         <v>50</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>47</v>
@@ -6465,13 +5837,13 @@
         <v>15</v>
       </c>
       <c r="L10" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="M10" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M10" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+    </row>
+    <row r="11" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>50</v>
       </c>
@@ -6479,16 +5851,16 @@
         <v>53</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>47</v>
@@ -6506,13 +5878,13 @@
         <v>15</v>
       </c>
       <c r="L11" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M11" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="M11" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+    </row>
+    <row r="12" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>50</v>
       </c>
@@ -6520,16 +5892,16 @@
         <v>57</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>47</v>
@@ -6547,13 +5919,13 @@
         <v>15</v>
       </c>
       <c r="L12" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="M12" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M12" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+    </row>
+    <row r="13" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>48</v>
       </c>
@@ -6561,16 +5933,16 @@
         <v>60</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>47</v>
@@ -6588,13 +5960,13 @@
         <v>15</v>
       </c>
       <c r="L13" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M13" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="M13" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+    </row>
+    <row r="14" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>60</v>
       </c>
@@ -6602,16 +5974,16 @@
         <v>63</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>47</v>
@@ -6629,30 +6001,30 @@
         <v>15</v>
       </c>
       <c r="L14" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="M14" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M14" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+    </row>
+    <row r="15" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>63</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>123</v>
+      <c r="C15" s="1">
+        <v>4.509E-3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>47</v>
@@ -6670,13 +6042,13 @@
         <v>15</v>
       </c>
       <c r="L15" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M15" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="M15" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+    </row>
+    <row r="16" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>66</v>
       </c>
@@ -6684,16 +6056,16 @@
         <v>69</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>47</v>
@@ -6711,13 +6083,13 @@
         <v>15</v>
       </c>
       <c r="L16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="M16" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M16" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+    </row>
+    <row r="17" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>69</v>
       </c>
@@ -6725,16 +6097,16 @@
         <v>72</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>47</v>
@@ -6752,13 +6124,13 @@
         <v>15</v>
       </c>
       <c r="L17" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M17" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="M17" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+    </row>
+    <row r="18" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>69</v>
       </c>
@@ -6766,16 +6138,16 @@
         <v>76</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>47</v>
@@ -6793,13 +6165,13 @@
         <v>15</v>
       </c>
       <c r="L18" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="M18" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M18" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+    </row>
+    <row r="19" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>76</v>
       </c>
@@ -6807,16 +6179,16 @@
         <v>16</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>47</v>
@@ -6834,13 +6206,13 @@
         <v>15</v>
       </c>
       <c r="L19" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M19" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="M19" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+    </row>
+    <row r="20" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>63</v>
       </c>
@@ -6848,16 +6220,16 @@
         <v>76</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>47</v>
@@ -6875,13 +6247,13 @@
         <v>15</v>
       </c>
       <c r="L20" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="M20" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M20" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+    </row>
+    <row r="21" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>66</v>
       </c>
@@ -6889,16 +6261,16 @@
         <v>16</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>47</v>
@@ -6916,689 +6288,688 @@
         <v>15</v>
       </c>
       <c r="L21" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M21" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="M21" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+    </row>
+    <row r="22" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:13" ht="15" x14ac:dyDescent="0.2">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A92" s="4"/>
       <c r="B92" s="4"/>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
     </row>
-    <row r="97" spans="1:2">
+    <row r="97" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
     </row>
-    <row r="98" spans="1:2">
+    <row r="98" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
     </row>
-    <row r="99" spans="1:2">
+    <row r="99" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
     </row>
-    <row r="100" spans="1:2">
+    <row r="100" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
     </row>
-    <row r="101" spans="1:2">
+    <row r="101" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
       <c r="B101" s="4"/>
     </row>
-    <row r="102" spans="1:2">
+    <row r="102" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A102" s="4"/>
       <c r="B102" s="4"/>
     </row>
-    <row r="103" spans="1:2">
+    <row r="103" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A103" s="4"/>
       <c r="B103" s="4"/>
     </row>
-    <row r="104" spans="1:2">
+    <row r="104" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A104" s="4"/>
       <c r="B104" s="4"/>
     </row>
-    <row r="105" spans="1:2">
+    <row r="105" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A105" s="4"/>
       <c r="B105" s="4"/>
     </row>
-    <row r="106" spans="1:2">
+    <row r="106" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A106" s="4"/>
       <c r="B106" s="4"/>
     </row>
-    <row r="107" spans="1:2">
+    <row r="107" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
     </row>
-    <row r="108" spans="1:2">
+    <row r="108" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
     </row>
-    <row r="109" spans="1:2">
+    <row r="109" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
     </row>
-    <row r="110" spans="1:2">
+    <row r="110" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A110" s="4"/>
       <c r="B110" s="4"/>
     </row>
-    <row r="111" spans="1:2">
+    <row r="111" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A111" s="4"/>
       <c r="B111" s="4"/>
     </row>
-    <row r="112" spans="1:2">
+    <row r="112" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A112" s="4"/>
       <c r="B112" s="4"/>
     </row>
-    <row r="113" spans="1:2">
+    <row r="113" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A113" s="4"/>
       <c r="B113" s="4"/>
     </row>
-    <row r="114" spans="1:2">
+    <row r="114" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
     </row>
-    <row r="115" spans="1:2">
+    <row r="115" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A115" s="4"/>
       <c r="B115" s="4"/>
     </row>
-    <row r="116" spans="1:2">
+    <row r="116" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
     </row>
-    <row r="117" spans="1:2">
+    <row r="117" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
     </row>
-    <row r="118" spans="1:2">
+    <row r="118" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
     </row>
-    <row r="119" spans="1:2">
+    <row r="119" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A119" s="4"/>
       <c r="B119" s="4"/>
     </row>
-    <row r="120" spans="1:2">
+    <row r="120" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
     </row>
-    <row r="121" spans="1:2">
+    <row r="121" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
     </row>
-    <row r="122" spans="1:2">
+    <row r="122" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A122" s="4"/>
       <c r="B122" s="4"/>
     </row>
-    <row r="123" spans="1:2">
+    <row r="123" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
     </row>
-    <row r="124" spans="1:2">
+    <row r="124" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
     </row>
-    <row r="125" spans="1:2">
+    <row r="125" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
     </row>
-    <row r="126" spans="1:2">
+    <row r="126" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A126" s="4"/>
       <c r="B126" s="4"/>
     </row>
-    <row r="127" spans="1:2">
+    <row r="127" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A127" s="4"/>
       <c r="B127" s="4"/>
     </row>
-    <row r="128" spans="1:2">
+    <row r="128" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
     </row>
-    <row r="129" spans="1:2">
+    <row r="129" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A129" s="4"/>
       <c r="B129" s="4"/>
     </row>
-    <row r="130" spans="1:2">
+    <row r="130" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A130" s="4"/>
       <c r="B130" s="4"/>
     </row>
-    <row r="131" spans="1:2">
+    <row r="131" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A131" s="4"/>
       <c r="B131" s="4"/>
     </row>
-    <row r="132" spans="1:2">
+    <row r="132" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A132" s="4"/>
       <c r="B132" s="4"/>
     </row>
-    <row r="133" spans="1:2">
+    <row r="133" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
     </row>
-    <row r="134" spans="1:2">
+    <row r="134" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A134" s="4"/>
       <c r="B134" s="4"/>
     </row>
-    <row r="135" spans="1:2">
+    <row r="135" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
     </row>
-    <row r="136" spans="1:2">
+    <row r="136" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
     </row>
-    <row r="137" spans="1:2">
+    <row r="137" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A137" s="4"/>
       <c r="B137" s="4"/>
     </row>
-    <row r="138" spans="1:2">
+    <row r="138" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A138" s="4"/>
       <c r="B138" s="4"/>
     </row>
-    <row r="139" spans="1:2">
+    <row r="139" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A139" s="4"/>
       <c r="B139" s="4"/>
     </row>
-    <row r="140" spans="1:2">
+    <row r="140" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A140" s="4"/>
       <c r="B140" s="4"/>
     </row>
-    <row r="141" spans="1:2">
+    <row r="141" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A141" s="4"/>
       <c r="B141" s="4"/>
     </row>
-    <row r="142" spans="1:2">
+    <row r="142" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
     </row>
-    <row r="143" spans="1:2">
+    <row r="143" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A143" s="4"/>
       <c r="B143" s="4"/>
     </row>
-    <row r="144" spans="1:2">
+    <row r="144" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A144" s="4"/>
       <c r="B144" s="4"/>
     </row>
-    <row r="145" spans="1:2">
+    <row r="145" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A145" s="4"/>
       <c r="B145" s="4"/>
     </row>
-    <row r="146" spans="1:2">
+    <row r="146" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A146" s="4"/>
       <c r="B146" s="4"/>
     </row>
-    <row r="147" spans="1:2">
+    <row r="147" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
     </row>
-    <row r="148" spans="1:2">
+    <row r="148" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
     </row>
-    <row r="149" spans="1:2">
+    <row r="149" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
     </row>
-    <row r="150" spans="1:2">
+    <row r="150" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A150" s="4"/>
       <c r="B150" s="4"/>
     </row>
-    <row r="151" spans="1:2">
+    <row r="151" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A151" s="4"/>
       <c r="B151" s="4"/>
     </row>
-    <row r="152" spans="1:2">
+    <row r="152" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
     </row>
-    <row r="153" spans="1:2">
+    <row r="153" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
     </row>
-    <row r="154" spans="1:2">
+    <row r="154" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
     </row>
-    <row r="155" spans="1:2">
+    <row r="155" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A155" s="4"/>
       <c r="B155" s="4"/>
     </row>
-    <row r="156" spans="1:2">
+    <row r="156" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
     </row>
-    <row r="157" spans="1:2">
+    <row r="157" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
     </row>
-    <row r="158" spans="1:2">
+    <row r="158" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
     </row>
-    <row r="159" spans="1:2">
+    <row r="159" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A159" s="4"/>
       <c r="B159" s="4"/>
     </row>
-    <row r="160" spans="1:2">
+    <row r="160" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A160" s="4"/>
       <c r="B160" s="4"/>
     </row>
-    <row r="161" spans="1:2">
+    <row r="161" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A161" s="4"/>
       <c r="B161" s="4"/>
     </row>
-    <row r="162" spans="1:2">
+    <row r="162" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A162" s="4"/>
       <c r="B162" s="4"/>
     </row>
-    <row r="163" spans="1:2">
+    <row r="163" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A163" s="4"/>
       <c r="B163" s="4"/>
     </row>
-    <row r="164" spans="1:2">
+    <row r="164" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A164" s="4"/>
       <c r="B164" s="4"/>
     </row>
-    <row r="165" spans="1:2">
+    <row r="165" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
     </row>
-    <row r="166" spans="1:2">
+    <row r="166" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A166" s="4"/>
       <c r="B166" s="4"/>
     </row>
-    <row r="167" spans="1:2">
+    <row r="167" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
     </row>
-    <row r="168" spans="1:2">
+    <row r="168" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A168" s="4"/>
       <c r="B168" s="4"/>
     </row>
-    <row r="169" spans="1:2">
+    <row r="169" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A169" s="4"/>
       <c r="B169" s="4"/>
     </row>
-    <row r="170" spans="1:2">
+    <row r="170" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A170" s="4"/>
       <c r="B170" s="4"/>
     </row>
-    <row r="171" spans="1:2">
+    <row r="171" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A171" s="4"/>
       <c r="B171" s="4"/>
     </row>
-    <row r="172" spans="1:2">
+    <row r="172" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A172" s="4"/>
       <c r="B172" s="4"/>
     </row>
-    <row r="173" spans="1:2">
+    <row r="173" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A173" s="4"/>
       <c r="B173" s="4"/>
     </row>
-    <row r="174" spans="1:2">
+    <row r="174" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A174" s="4"/>
       <c r="B174" s="4"/>
     </row>
-    <row r="175" spans="1:2">
+    <row r="175" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
     </row>
-    <row r="176" spans="1:2">
+    <row r="176" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A176" s="4"/>
       <c r="B176" s="4"/>
     </row>
-    <row r="177" spans="1:2">
+    <row r="177" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
     </row>
-    <row r="178" spans="1:2">
+    <row r="178" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
     </row>
-    <row r="179" spans="1:2">
+    <row r="179" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A179" s="4"/>
       <c r="B179" s="4"/>
     </row>
-    <row r="180" spans="1:2">
+    <row r="180" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
     </row>
-    <row r="181" spans="1:2">
+    <row r="181" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
     </row>
-    <row r="182" spans="1:2">
+    <row r="182" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A182" s="4"/>
       <c r="B182" s="4"/>
     </row>
-    <row r="183" spans="1:2">
+    <row r="183" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A183" s="4"/>
       <c r="B183" s="4"/>
     </row>
-    <row r="184" spans="1:2">
+    <row r="184" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
     </row>
-    <row r="185" spans="1:2">
+    <row r="185" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A185" s="4"/>
       <c r="B185" s="4"/>
     </row>
-    <row r="186" spans="1:2">
+    <row r="186" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A186" s="4"/>
       <c r="B186" s="4"/>
     </row>
-    <row r="187" spans="1:2">
+    <row r="187" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A187" s="4"/>
       <c r="B187" s="4"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:X55"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:24" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
@@ -7609,22 +6980,22 @@
         <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>17</v>
@@ -7654,33 +7025,33 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>17</v>
@@ -7716,7 +7087,7 @@
       <c r="W2" s="4"/>
       <c r="X2" s="4"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>48</v>
       </c>
@@ -7727,22 +7098,22 @@
         <v>17</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>17</v>
@@ -7778,7 +7149,7 @@
       <c r="W3" s="4"/>
       <c r="X3" s="4"/>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -7804,204 +7175,203 @@
       <c r="W4" s="4"/>
       <c r="X4" s="4"/>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:24" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="4"/>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:24" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="4"/>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:24" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:24" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:24" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:24" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="4"/>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:24" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="4"/>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:24" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="4"/>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:24" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="4"/>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:24" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="4"/>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:24" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="4"/>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:24" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="4"/>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="4"/>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="4"/>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="4"/>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="4"/>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="4"/>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A26" s="4"/>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A27" s="4"/>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A28" s="4"/>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A30" s="4"/>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A31" s="4"/>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A32" s="4"/>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A33" s="4"/>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A34" s="4"/>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A35" s="4"/>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A38" s="4"/>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A39" s="4"/>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A40" s="4"/>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A41" s="4"/>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A42" s="4"/>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="4"/>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="4"/>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A45" s="4"/>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="4"/>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A47" s="4"/>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A48" s="4"/>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A49" s="4"/>
     </row>
-    <row r="50" spans="1:1">
+    <row r="50" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A50" s="4"/>
     </row>
-    <row r="51" spans="1:1">
+    <row r="51" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A51" s="4"/>
     </row>
-    <row r="52" spans="1:1">
+    <row r="52" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A52" s="4"/>
     </row>
-    <row r="53" spans="1:1">
+    <row r="53" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A53" s="4"/>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A54" s="4"/>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55" spans="1:1" ht="15" x14ac:dyDescent="0.2">
       <c r="A55" s="4"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
       <c r="B2" s="2">
         <v>1.3</v>
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>200</v>
@@ -8011,58 +7381,57 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="6" max="6" width="9.66666666666667"/>
+    <col min="6" max="6" width="9.625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+    </row>
+    <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>100</v>
       </c>
       <c r="B2" s="3">
-        <v>-0.003</v>
+        <v>-3.0000000000000001E-3</v>
       </c>
       <c r="C2" s="3">
-        <v>-1e-5</v>
+        <v>-1.0000000000000001E-5</v>
       </c>
       <c r="D2" s="3">
         <v>0.03</v>
@@ -8071,46 +7440,45 @@
         <v>0.35</v>
       </c>
       <c r="F2" s="3">
-        <v>-0.000327</v>
+        <v>-3.2699999999999998E-4</v>
       </c>
       <c r="G2" s="3">
         <v>0.183</v>
       </c>
       <c r="H2" s="3">
-        <v>0.0139</v>
+        <v>1.3899999999999999E-2</v>
       </c>
       <c r="I2" s="3">
-        <v>-5.82e-5</v>
+        <v>-5.8199999999999998E-5</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
       <c r="B2" s="2">
         <v>0.8</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>